--- a/tests/fixtures/test-payroll.xlsx
+++ b/tests/fixtures/test-payroll.xlsx
@@ -3748,7 +3748,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">

--- a/tests/fixtures/test-payroll.xlsx
+++ b/tests/fixtures/test-payroll.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA49"/>
+  <dimension ref="A1:AA50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2703,37 +2703,37 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Hana Kimura</t>
+          <t>Pearl Adeyemi</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2743,27 +2743,22 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>210.00</t>
+          <t>175.00</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>168.00</t>
+          <t>115.00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>42.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>41.04</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>50.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2773,7 +2768,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>210.00</t>
+          <t>175.00</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2788,16 +2783,16 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95001</v>
+        <v>90020</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01TEST95001</t>
+          <t>01TEST90020</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Test Family</t>
+          <t>Care Family</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2812,7 +2807,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Babysitter</t>
+          <t>Corporate (Invoiced)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2828,37 +2823,37 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Cleo Barnes</t>
+          <t>Hana Kimura</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2868,17 +2863,27 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>210.00</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>115.00</t>
+          <t>168.00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>42.00</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>41.04</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>50.00</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -2888,7 +2893,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>210.00</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3018,11 +3023,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>90022</v>
+        <v>95001</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01TEST90022</t>
+          <t>01TEST95001</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3058,7 +3063,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3068,7 +3073,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3083,7 +3088,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Ada Whitlow</t>
+          <t>Cleo Barnes</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3178,7 +3183,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3188,12 +3193,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3213,17 +3218,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>140.00</t>
+          <t>175.00</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>92.00</t>
+          <t>115.00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3233,7 +3238,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>140.00</t>
+          <t>175.00</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3288,22 +3293,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3313,7 +3318,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>June Salter</t>
+          <t>Ada Whitlow</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3333,12 +3338,12 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>99.99</t>
+          <t>92.00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>40.01</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3403,37 +3408,37 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Belle Cruz</t>
+          <t>June Salter</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3448,12 +3453,12 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>92.00</t>
+          <t>99.99</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>40.01</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3518,37 +3523,37 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Opal Grant</t>
+          <t>Belle Cruz</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3558,17 +3563,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>210.00</t>
+          <t>140.00</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>138.00</t>
+          <t>92.00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>72.00</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3578,7 +3583,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>210.00</t>
+          <t>140.00</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3593,11 +3598,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>95500</v>
+        <v>90027</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01TEST95500</t>
+          <t>01TEST90027</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3633,32 +3638,32 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Vera Lund</t>
+          <t>Opal Grant</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3673,17 +3678,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>210.00</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>115.00</t>
+          <t>138.00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>72.00</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -3693,7 +3698,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>210.00</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3708,11 +3713,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>90028</v>
+        <v>95500</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01TEST90028</t>
+          <t>01TEST95500</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3748,32 +3753,32 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Ruth Ozeki</t>
+          <t>Vera Lund</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3788,17 +3793,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>140.00</t>
+          <t>175.00</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>92.00</t>
+          <t>115.00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -3808,7 +3813,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>140.00</t>
+          <t>175.00</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3863,7 +3868,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3873,7 +3878,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3978,7 +3983,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3988,7 +3993,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4093,7 +4098,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4103,7 +4108,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4208,7 +4213,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4218,7 +4223,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4323,7 +4328,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4333,7 +4338,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4438,7 +4443,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4448,7 +4453,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4553,7 +4558,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4563,22 +4568,22 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Cass Moreau</t>
+          <t>Ruth Ozeki</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4593,17 +4598,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>245.00</t>
+          <t>140.00</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>161.00</t>
+          <t>92.00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>84.00</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -4613,7 +4618,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>245.00</t>
+          <t>140.00</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4668,7 +4673,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4678,7 +4683,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4783,7 +4788,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4793,7 +4798,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4898,7 +4903,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4908,7 +4913,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -5013,7 +5018,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5023,7 +5028,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5128,7 +5133,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5138,7 +5143,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -5243,32 +5248,32 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Lena Voss</t>
+          <t>Cass Moreau</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5283,17 +5288,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>315.00</t>
+          <t>245.00</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>207.00</t>
+          <t>161.00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>108.00</t>
+          <t>84.00</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5303,7 +5308,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>315.00</t>
+          <t>245.00</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -5313,7 +5318,7 @@
       </c>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -5358,57 +5363,57 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Rosa Delgado</t>
+          <t>Lena Voss</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>charged</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>315.00</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>115.00</t>
+          <t>207.00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>108.00</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -5418,7 +5423,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>315.00</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -5428,7 +5433,7 @@
       </c>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
@@ -5473,7 +5478,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5483,7 +5488,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5503,7 +5508,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -5557,7 +5562,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nobody Assigned</t>
+          <t>Test Family</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5611,15 +5616,19 @@
           <t>5.00</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Rosa Delgado</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>charged</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -5668,7 +5677,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Test Test</t>
+          <t>Nobody Assigned</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5699,7 +5708,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5709,24 +5718,20 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Zed Tester</t>
-        </is>
-      </c>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>completed</t>
@@ -5739,17 +5744,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>140.00</t>
+          <t>175.00</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>92.00</t>
+          <t>115.00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -5759,7 +5764,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>140.00</t>
+          <t>175.00</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5783,7 +5788,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Test Family</t>
+          <t>Test Test</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5814,7 +5819,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5824,22 +5829,22 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Rosa Delgado</t>
+          <t>Zed Tester</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5854,17 +5859,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>140.00</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>115.00</t>
+          <t>92.00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -5874,7 +5879,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>140.00</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5929,7 +5934,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5939,22 +5944,22 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Ivy Chen</t>
+          <t>Rosa Delgado</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5969,17 +5974,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>210.00</t>
+          <t>175.00</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>168.00</t>
+          <t>115.00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>42.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -5989,7 +5994,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>210.00</t>
+          <t>175.00</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -6013,7 +6018,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Care Family</t>
+          <t>Test Family</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6028,7 +6033,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Corporate (Invoiced)</t>
+          <t>Babysitter</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6044,7 +6049,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6054,22 +6059,22 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Gwen Mabry</t>
+          <t>Ivy Chen</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6084,22 +6089,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>210.00</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>115.00</t>
+          <t>168.00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>60.00</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>29.00</t>
+          <t>42.00</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>210.00</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -6119,6 +6119,126 @@
       </c>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>90049</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>01TEST90049</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Care Family</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>family@example.com</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>+16195550000</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Corporate (Invoiced)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Private Home</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1 Test Way, San Diego, CA, 92101</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Gwen Mabry</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>charged</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>115.00</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>29.00</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:00</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="n">
         <v>0</v>
       </c>
     </row>

--- a/tests/fixtures/test-payroll.xlsx
+++ b/tests/fixtures/test-payroll.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA50"/>
+  <dimension ref="A1:AM51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,125 +429,185 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Care.com Job Number</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Client Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Client Email</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Client Phone</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Service Type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Location Type</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Hotel</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Start Time</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>End Time</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Total Hours</t>
-        </is>
-      </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>Hours Worked</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Hours Billed</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Minimum Applied</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Caregiver ID</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>Caregiver Name</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>OnPay Clock User</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Payment Status</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Charge to Client</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Paid to Caregiver</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Pay Rate</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Sitterwise Cut</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Reimbursement Description</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Round Trip Miles</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Mileage Approved Miles</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Mileage Approval Status</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Payable Miles</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Mileage Amount</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Tip</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Bonus</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Total Amount</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Created At</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Admin Notes</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Lifesaver Bonus</t>
         </is>
@@ -562,109 +622,137 @@
           <t>01TEST90001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>Rosa Delgado</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>115.00</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AB2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -677,109 +765,137 @@
           <t>01TEST90002</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>Rosa Delgado</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>115.00</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AB3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -792,109 +908,137 @@
           <t>01TEST90003</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>Rosa Delgado</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>115.00</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AB4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="n">
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -907,109 +1051,137 @@
           <t>01TEST90004</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Big Family</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>6.00</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>Ivy Chen</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>210.00</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>168.00</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>42.00</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AB5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>210.00</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="n">
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1022,109 +1194,137 @@
           <t>01TEST90005</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Big Family</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>6.00</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>Ivy Chen</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>210.00</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>168.00</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>42.00</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AB6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>210.00</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="n">
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1137,109 +1337,137 @@
           <t>01TEST90006</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>6.00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>Mona Patel</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>210.00</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>138.00</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>72.00</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AB7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>210.00</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="n">
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1252,109 +1480,137 @@
           <t>01TEST90007</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Big Family</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>Mona Patel</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>112.00</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>28.00</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="n">
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1367,109 +1623,137 @@
           <t>01TEST90008</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>Dana Reyes</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>350.00</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>230.00</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>120.00</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AB9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>350.00</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="AK9" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="n">
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1482,109 +1766,137 @@
           <t>01TEST90009</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>Dana Reyes</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>92.00</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>48.00</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AB10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="n">
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1597,109 +1909,137 @@
           <t>01TEST90010</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>Tess Okafor</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>115.00</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="AB11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="AK11" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="n">
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1712,109 +2052,137 @@
           <t>01TEST90011</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Big Family</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>Tess Okafor</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>35.00</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="AB12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="AK12" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="n">
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1827,113 +2195,141 @@
           <t>01TEST90012</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Hotel</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Hotel del Coronado</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>13.00</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>Priya Raman</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>455.00</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>299.00</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>156.00</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="AB13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="AJ13" t="inlineStr">
         <is>
           <t>455.00</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="AK13" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="n">
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1946,114 +2342,142 @@
           <t>01TEST90013</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>Nina Alvarez</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
         <is>
           <t>paid</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>92.00</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>48.00</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="AB14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>75.00</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="AK14" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="n">
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2068,116 +2492,167 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>5512001</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Care Family</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Corporate (Invoiced)</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>Gwen Mabry</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>115.00</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>30.40</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>mileage</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>30.40</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="AJ15" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="AK15" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AL15" t="inlineStr">
         <is>
           <t>Drove to Carlsbad</t>
         </is>
       </c>
-      <c r="AA15" t="n">
+      <c r="AM15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2190,114 +2665,146 @@
           <t>01TEST90015</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>Sofia Bright</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>92.00</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>48.00</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>22.50</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Ace parking, no street parking available</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="AK16" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="n">
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2310,114 +2817,142 @@
           <t>01TEST90016</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>Faye Nakamura</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>115.00</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>30.40</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="AB17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="AK17" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="n">
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2432,112 +2967,163 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>5512003</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>Care Family</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Corporate (Invoiced)</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>Della Cruz</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>92.00</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>48.00</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>76.00</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>45.60</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>mileage</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>45.60</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="AK18" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="n">
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2552,112 +3138,163 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>5512006</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>Care Family</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Corporate (Invoiced)</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Nadia Okoro</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Blythe Ferrer</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>92.00</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>48.00</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>15.20</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>76.00</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>mileage</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>76.00</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="AJ19" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="AK19" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="n">
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2672,112 +3309,163 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>5512004</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>Care Family</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Corporate (Invoiced)</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Pearl Adeyemi</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Nadia Okoro</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>115.00</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
       <c r="W20" t="inlineStr">
         <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>92.00</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>48.00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>15.20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>mileage</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>15.20</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="n">
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2792,232 +3480,324 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>5512005</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>Care Family</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Corporate (Invoiced)</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Hana Kimura</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Pearl Adeyemi</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>210.00</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>168.00</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>41.04</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>115.00</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>mileage</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>210.00</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="n">
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>95001</v>
+        <v>90021</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01TEST95001</t>
+          <t>01TEST90021</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Test Family</t>
+          <t>5512002</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>Care Family</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Babysitter</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>Corporate (Invoiced)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Cleo Barnes</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Hana Kimura</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>115.00</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
-      </c>
       <c r="W22" t="inlineStr">
         <is>
+          <t>210.00</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>168.00</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>42.00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>41.04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>mileage</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>41.04</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>210.00</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="n">
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3030,224 +3810,280 @@
           <t>01TEST95001</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>Cleo Barnes</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>115.00</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="AB23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="AJ23" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="AK23" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="n">
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>90023</v>
+        <v>95001</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01TEST90023</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+          <t>01TEST95001</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Ada Whitlow</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Cleo Barnes</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>115.00</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="AB24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="AJ24" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="AK24" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="n">
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3260,109 +4096,137 @@
           <t>01TEST90024</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
           <t>Ada Whitlow</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>92.00</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>48.00</t>
-        </is>
-      </c>
       <c r="W25" t="inlineStr">
         <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>115.00</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="n">
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3375,109 +4239,137 @@
           <t>01TEST90025</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>June Salter</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Ada Whitlow</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>99.99</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>40.01</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>92.00</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>48.00</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="AJ26" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="AK26" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="n">
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3490,109 +4382,133 @@
           <t>01TEST90026</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Belle Cruz</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>June Salter</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>92.00</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>48.00</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>99.99</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>40.01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="AJ27" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="AK27" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="n">
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3605,339 +4521,423 @@
           <t>01TEST90027</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Opal Grant</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Belle Cruz</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>210.00</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>138.00</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>72.00</t>
-        </is>
-      </c>
       <c r="W28" t="inlineStr">
         <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>92.00</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>48.00</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>210.00</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="n">
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>95500</v>
+        <v>90028</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01TEST95500</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+          <t>01TEST90028</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Vera Lund</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Opal Grant</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>115.00</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
-      </c>
       <c r="W29" t="inlineStr">
         <is>
+          <t>210.00</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>138.00</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>72.00</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>210.00</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="n">
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>90029</v>
+        <v>95500</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01TEST90029</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+          <t>01TEST95500</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Ruth Ozeki</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Vera Lund</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>92.00</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>48.00</t>
-        </is>
-      </c>
       <c r="W30" t="inlineStr">
         <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>115.00</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="n">
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3950,109 +4950,137 @@
           <t>01TEST90030</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="M31" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
         <is>
           <t>Ruth Ozeki</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>92.00</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
         <is>
           <t>48.00</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="AB31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="AJ31" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="AK31" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="n">
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4065,109 +5093,137 @@
           <t>01TEST90031</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="M32" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
         <is>
           <t>Ruth Ozeki</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>92.00</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>48.00</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="AB32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="AJ32" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="AK32" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="n">
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4180,109 +5236,137 @@
           <t>01TEST90032</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
       <c r="M33" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>Ruth Ozeki</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>92.00</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
         <is>
           <t>48.00</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="AB33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="AJ33" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="AK33" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="n">
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4295,109 +5379,137 @@
           <t>01TEST90033</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
         <is>
           <t>Ruth Ozeki</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>92.00</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>48.00</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="AB34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="AJ34" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="AK34" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="n">
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4410,109 +5522,137 @@
           <t>01TEST90034</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
       <c r="M35" t="inlineStr">
         <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
         <is>
           <t>Ruth Ozeki</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>92.00</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
         <is>
           <t>48.00</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="AB35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="AJ35" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="AK35" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="n">
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4525,109 +5665,137 @@
           <t>01TEST90035</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
       <c r="M36" t="inlineStr">
         <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
         <is>
           <t>Ruth Ozeki</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>92.00</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
         <is>
           <t>48.00</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="AB36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="AJ36" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="AK36" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="n">
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4640,109 +5808,137 @@
           <t>01TEST90036</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Cass Moreau</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Ruth Ozeki</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>245.00</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>161.00</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>84.00</t>
-        </is>
-      </c>
       <c r="W37" t="inlineStr">
         <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>92.00</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>48.00</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>245.00</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="n">
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4755,109 +5951,137 @@
           <t>01TEST90037</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="M38" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>7.00</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
         <is>
           <t>Cass Moreau</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>245.00</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>161.00</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
         <is>
           <t>84.00</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="AB38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="AJ38" t="inlineStr">
         <is>
           <t>245.00</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="AK38" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="n">
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4870,109 +6094,137 @@
           <t>01TEST90038</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="M39" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>7.00</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
         <is>
           <t>Cass Moreau</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>245.00</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>161.00</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
         <is>
           <t>84.00</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="AB39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="AJ39" t="inlineStr">
         <is>
           <t>245.00</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="AK39" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="n">
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4985,109 +6237,137 @@
           <t>01TEST90039</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
       <c r="M40" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>7.00</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
         <is>
           <t>Cass Moreau</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>245.00</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>161.00</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
         <is>
           <t>84.00</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="AB40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="AJ40" t="inlineStr">
         <is>
           <t>245.00</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="AK40" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="n">
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5100,109 +6380,137 @@
           <t>01TEST90040</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
       <c r="M41" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>7.00</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
         <is>
           <t>Cass Moreau</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>245.00</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>161.00</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
         <is>
           <t>84.00</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="AB41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="AJ41" t="inlineStr">
         <is>
           <t>245.00</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="AK41" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="n">
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5215,109 +6523,137 @@
           <t>01TEST90041</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
       <c r="M42" t="inlineStr">
         <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>7.00</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
         <is>
           <t>Cass Moreau</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>245.00</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>161.00</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
         <is>
           <t>84.00</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="AB42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="AJ42" t="inlineStr">
         <is>
           <t>245.00</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="AK42" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="n">
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5330,110 +6666,138 @@
           <t>01TEST90042</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Lena Voss</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Cass Moreau</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>315.00</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>207.00</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>108.00</t>
-        </is>
-      </c>
       <c r="W43" t="inlineStr">
         <is>
+          <t>245.00</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>161.00</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>84.00</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>315.00</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>245.00</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="n">
-        <v>15</v>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -5445,110 +6809,138 @@
           <t>01TEST90043</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Rosa Delgado</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>False</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>991</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>115.00</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>60.00</t>
+          <t>Lena Voss</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>charged</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
+          <t>315.00</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>207.00</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>108.00</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>315.00</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="n">
-        <v>0</v>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="45">
@@ -5560,109 +6952,137 @@
           <t>01TEST90044</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="M45" t="inlineStr">
         <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
         <is>
           <t>Rosa Delgado</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>115.00</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="AB45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="AJ45" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="AK45" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="n">
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5675,105 +7095,137 @@
           <t>01TEST90045</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Nobody Assigned</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
+          <t>Test Family</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>charged</t>
+          <t>False</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Rosa Delgado</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>115.00</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="AB46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="AJ46" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="AK46" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="n">
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5786,109 +7238,129 @@
           <t>01TEST90046</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Test Test</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
+          <t>Nobody Assigned</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Zed Tester</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>92.00</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>48.00</t>
-        </is>
-      </c>
       <c r="W47" t="inlineStr">
         <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>115.00</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="n">
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5901,109 +7373,137 @@
           <t>01TEST90047</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Test Family</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
+          <t>Test Test</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Rosa Delgado</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Zed Tester</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>115.00</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
-      </c>
       <c r="W48" t="inlineStr">
         <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>92.00</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>48.00</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="n">
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6016,109 +7516,137 @@
           <t>01TEST90048</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
         <is>
           <t>Test Family</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Babysitter</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Ivy Chen</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Rosa Delgado</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>210.00</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>168.00</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
-      </c>
       <c r="W49" t="inlineStr">
         <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>115.00</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>210.00</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="n">
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6131,114 +7659,304 @@
           <t>01TEST90049</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Test Family</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>family@example.com</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>+16195550000</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Babysitter</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Private Home</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1 Test Way, San Diego, CA, 92101</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Ivy Chen</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>charged</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>210.00</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>168.00</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>42.00</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>210.00</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:00</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>90050</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>01TEST90050</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
         <is>
           <t>Care Family</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>family@example.com</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>+16195550000</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Corporate (Invoiced)</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Private Home</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
         <is>
           <t>1 Test Way, San Diego, CA, 92101</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
         <is>
           <t>Gwen Mabry</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>charged</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>115.00</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>29.00</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>mileage</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>29.00</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="AJ51" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="AK51" t="inlineStr">
         <is>
           <t>2026-07-20 09:00</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="n">
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="n">
         <v>0</v>
       </c>
     </row>
